--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2713,6 +2713,578 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126287775</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>460619</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6989872</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bitvis talrika förekomster, finns spritt i större delen av området. Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126287460</v>
+      </c>
+      <c r="B23" t="n">
+        <v>75068</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>460522</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6989883</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126287351</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98366</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>460494</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6989828</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bitvis talrika förekomster, finns spritt i större delen av området. Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126287535</v>
+      </c>
+      <c r="B25" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>460539</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6989868</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126287420</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>460597</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6989850</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -2718,7 +2718,7 @@
         <v>126287775</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>126287460</v>
       </c>
       <c r="B23" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126287351</v>
       </c>
       <c r="B24" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>126287535</v>
       </c>
       <c r="B25" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>126287420</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -2718,7 +2718,7 @@
         <v>126287775</v>
       </c>
       <c r="B22" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126287351</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -2718,7 +2718,7 @@
         <v>126287775</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>126287460</v>
       </c>
       <c r="B23" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126287351</v>
       </c>
       <c r="B24" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>126287535</v>
       </c>
       <c r="B25" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>126287420</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3290,7 +3290,7 @@
         <v>127028746</v>
       </c>
       <c r="B27" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>127028704</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028716</v>
+        <v>127028668</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460382</v>
+        <v>460442</v>
       </c>
       <c r="R29" t="n">
-        <v>6990158</v>
+        <v>6990074</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028668</v>
+        <v>127028716</v>
       </c>
       <c r="B30" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460442</v>
+        <v>460382</v>
       </c>
       <c r="R30" t="n">
-        <v>6990074</v>
+        <v>6990158</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3678,7 +3678,7 @@
         <v>127028721</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>127028719</v>
       </c>
       <c r="B32" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,32 +3869,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127028680</v>
+        <v>127028687</v>
       </c>
       <c r="B33" t="n">
-        <v>98382</v>
+        <v>80114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460426</v>
+        <v>460422</v>
       </c>
       <c r="R33" t="n">
-        <v>6990076</v>
+        <v>6990185</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3940,6 +3940,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3966,32 +3971,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127028687</v>
+        <v>127028680</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>98457</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4001,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460422</v>
+        <v>460426</v>
       </c>
       <c r="R34" t="n">
-        <v>6990185</v>
+        <v>6990076</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4037,11 +4042,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4071,7 +4071,7 @@
         <v>127028702</v>
       </c>
       <c r="B35" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>127028731</v>
       </c>
       <c r="B36" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>127028631</v>
       </c>
       <c r="B37" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>127028700</v>
       </c>
       <c r="B38" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4456,32 +4456,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028632</v>
+        <v>127028658</v>
       </c>
       <c r="B39" t="n">
-        <v>80083</v>
+        <v>98457</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460580</v>
+        <v>460450</v>
       </c>
       <c r="R39" t="n">
-        <v>6990068</v>
+        <v>6989987</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4556,7 +4556,7 @@
         <v>127028693</v>
       </c>
       <c r="B40" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028658</v>
+        <v>127028632</v>
       </c>
       <c r="B41" t="n">
-        <v>98382</v>
+        <v>80114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460450</v>
+        <v>460580</v>
       </c>
       <c r="R41" t="n">
-        <v>6989987</v>
+        <v>6990068</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4747,10 +4747,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127028647</v>
+        <v>127028726</v>
       </c>
       <c r="B42" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460528</v>
+        <v>460354</v>
       </c>
       <c r="R42" t="n">
-        <v>6990066</v>
+        <v>6989926</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127028726</v>
+        <v>127028647</v>
       </c>
       <c r="B43" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460354</v>
+        <v>460528</v>
       </c>
       <c r="R43" t="n">
-        <v>6989926</v>
+        <v>6990066</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4944,7 +4944,7 @@
         <v>127028734</v>
       </c>
       <c r="B44" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>127028626</v>
       </c>
       <c r="B45" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>127028692</v>
       </c>
       <c r="B46" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028750</v>
+        <v>127028755</v>
       </c>
       <c r="B47" t="n">
-        <v>80084</v>
+        <v>98457</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460302</v>
+        <v>460239</v>
       </c>
       <c r="R47" t="n">
-        <v>6990069</v>
+        <v>6990025</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028634</v>
+        <v>127028750</v>
       </c>
       <c r="B48" t="n">
-        <v>80083</v>
+        <v>80115</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5340,21 +5340,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460576</v>
+        <v>460302</v>
       </c>
       <c r="R48" t="n">
-        <v>6990197</v>
+        <v>6990069</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5426,32 +5426,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127028755</v>
+        <v>127028634</v>
       </c>
       <c r="B49" t="n">
-        <v>98382</v>
+        <v>80114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460239</v>
+        <v>460576</v>
       </c>
       <c r="R49" t="n">
-        <v>6990025</v>
+        <v>6990197</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5526,7 +5526,7 @@
         <v>127028682</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>127028737</v>
       </c>
       <c r="B51" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>127028741</v>
       </c>
       <c r="B52" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5814,32 +5814,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028711</v>
+        <v>127028723</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>80114</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460385</v>
+        <v>460357</v>
       </c>
       <c r="R53" t="n">
-        <v>6990183</v>
+        <v>6989952</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,10 +5911,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028723</v>
+        <v>127028695</v>
       </c>
       <c r="B54" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460357</v>
+        <v>460416</v>
       </c>
       <c r="R54" t="n">
-        <v>6989952</v>
+        <v>6990144</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6008,32 +6008,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127028695</v>
+        <v>127028711</v>
       </c>
       <c r="B55" t="n">
-        <v>80083</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460416</v>
+        <v>460385</v>
       </c>
       <c r="R55" t="n">
-        <v>6990144</v>
+        <v>6990183</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3290,7 +3290,7 @@
         <v>127028746</v>
       </c>
       <c r="B27" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>127028704</v>
       </c>
       <c r="B28" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>127028668</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>127028716</v>
       </c>
       <c r="B30" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>127028721</v>
       </c>
       <c r="B31" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>127028719</v>
       </c>
       <c r="B32" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>127028687</v>
       </c>
       <c r="B33" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>127028680</v>
       </c>
       <c r="B34" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>127028702</v>
       </c>
       <c r="B35" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>127028731</v>
       </c>
       <c r="B36" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127028631</v>
+        <v>127028632</v>
       </c>
       <c r="B37" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4300,7 +4300,7 @@
         <v>460580</v>
       </c>
       <c r="R37" t="n">
-        <v>6990166</v>
+        <v>6990068</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4359,32 +4359,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127028700</v>
+        <v>127028631</v>
       </c>
       <c r="B38" t="n">
-        <v>98457</v>
+        <v>98442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460399</v>
+        <v>460580</v>
       </c>
       <c r="R38" t="n">
-        <v>6990025</v>
+        <v>6990166</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4456,32 +4456,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028658</v>
+        <v>127028693</v>
       </c>
       <c r="B39" t="n">
-        <v>98457</v>
+        <v>80117</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460450</v>
+        <v>460419</v>
       </c>
       <c r="R39" t="n">
-        <v>6989987</v>
+        <v>6990129</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028693</v>
+        <v>127028658</v>
       </c>
       <c r="B40" t="n">
-        <v>80114</v>
+        <v>98463</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460419</v>
+        <v>460450</v>
       </c>
       <c r="R40" t="n">
-        <v>6990129</v>
+        <v>6989987</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028632</v>
+        <v>127028700</v>
       </c>
       <c r="B41" t="n">
-        <v>80114</v>
+        <v>98463</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460580</v>
+        <v>460399</v>
       </c>
       <c r="R41" t="n">
-        <v>6990068</v>
+        <v>6990025</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4747,10 +4747,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127028726</v>
+        <v>127028647</v>
       </c>
       <c r="B42" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460354</v>
+        <v>460528</v>
       </c>
       <c r="R42" t="n">
-        <v>6989926</v>
+        <v>6990066</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127028647</v>
+        <v>127028726</v>
       </c>
       <c r="B43" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460528</v>
+        <v>460354</v>
       </c>
       <c r="R43" t="n">
-        <v>6990066</v>
+        <v>6989926</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4944,7 +4944,7 @@
         <v>127028734</v>
       </c>
       <c r="B44" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>127028626</v>
       </c>
       <c r="B45" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5135,32 +5135,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028692</v>
+        <v>127028634</v>
       </c>
       <c r="B46" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460419</v>
+        <v>460576</v>
       </c>
       <c r="R46" t="n">
-        <v>6990164</v>
+        <v>6990197</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028755</v>
+        <v>127028750</v>
       </c>
       <c r="B47" t="n">
-        <v>98457</v>
+        <v>80118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460239</v>
+        <v>460302</v>
       </c>
       <c r="R47" t="n">
-        <v>6990025</v>
+        <v>6990069</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5329,32 +5329,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028750</v>
+        <v>127028692</v>
       </c>
       <c r="B48" t="n">
-        <v>80115</v>
+        <v>98442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460302</v>
+        <v>460419</v>
       </c>
       <c r="R48" t="n">
-        <v>6990069</v>
+        <v>6990164</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5426,32 +5426,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127028634</v>
+        <v>127028755</v>
       </c>
       <c r="B49" t="n">
-        <v>80114</v>
+        <v>98463</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460576</v>
+        <v>460239</v>
       </c>
       <c r="R49" t="n">
-        <v>6990197</v>
+        <v>6990025</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5526,7 +5526,7 @@
         <v>127028682</v>
       </c>
       <c r="B50" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>127028737</v>
       </c>
       <c r="B51" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>127028741</v>
       </c>
       <c r="B52" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5814,32 +5814,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028723</v>
+        <v>127028711</v>
       </c>
       <c r="B53" t="n">
-        <v>80114</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460357</v>
+        <v>460385</v>
       </c>
       <c r="R53" t="n">
-        <v>6989952</v>
+        <v>6990183</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,10 +5911,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028695</v>
+        <v>127028723</v>
       </c>
       <c r="B54" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460416</v>
+        <v>460357</v>
       </c>
       <c r="R54" t="n">
-        <v>6990144</v>
+        <v>6989952</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6008,32 +6008,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127028711</v>
+        <v>127028695</v>
       </c>
       <c r="B55" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460385</v>
+        <v>460416</v>
       </c>
       <c r="R55" t="n">
-        <v>6990183</v>
+        <v>6990144</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3481,7 +3481,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028668</v>
+        <v>127028721</v>
       </c>
       <c r="B29" t="n">
         <v>98442</v>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460442</v>
+        <v>460361</v>
       </c>
       <c r="R29" t="n">
         <v>6990074</v>
@@ -3578,7 +3578,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028716</v>
+        <v>127028668</v>
       </c>
       <c r="B30" t="n">
         <v>98442</v>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460382</v>
+        <v>460442</v>
       </c>
       <c r="R30" t="n">
-        <v>6990158</v>
+        <v>6990074</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3675,7 +3675,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127028721</v>
+        <v>127028716</v>
       </c>
       <c r="B31" t="n">
         <v>98442</v>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460361</v>
+        <v>460382</v>
       </c>
       <c r="R31" t="n">
-        <v>6990074</v>
+        <v>6990158</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127028632</v>
+        <v>127028631</v>
       </c>
       <c r="B37" t="n">
-        <v>80117</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4300,7 +4300,7 @@
         <v>460580</v>
       </c>
       <c r="R37" t="n">
-        <v>6990068</v>
+        <v>6990166</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4359,32 +4359,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127028631</v>
+        <v>127028658</v>
       </c>
       <c r="B38" t="n">
-        <v>98442</v>
+        <v>98463</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460580</v>
+        <v>460450</v>
       </c>
       <c r="R38" t="n">
-        <v>6990166</v>
+        <v>6989987</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4456,32 +4456,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028693</v>
+        <v>127028700</v>
       </c>
       <c r="B39" t="n">
-        <v>80117</v>
+        <v>98463</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460419</v>
+        <v>460399</v>
       </c>
       <c r="R39" t="n">
-        <v>6990129</v>
+        <v>6990025</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028658</v>
+        <v>127028693</v>
       </c>
       <c r="B40" t="n">
-        <v>98463</v>
+        <v>80117</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460450</v>
+        <v>460419</v>
       </c>
       <c r="R40" t="n">
-        <v>6989987</v>
+        <v>6990129</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028700</v>
+        <v>127028632</v>
       </c>
       <c r="B41" t="n">
-        <v>98463</v>
+        <v>80117</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460399</v>
+        <v>460580</v>
       </c>
       <c r="R41" t="n">
-        <v>6990025</v>
+        <v>6990068</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5620,32 +5620,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127028737</v>
+        <v>127028741</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>98463</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>460333</v>
+        <v>460325</v>
       </c>
       <c r="R51" t="n">
-        <v>6990071</v>
+        <v>6990076</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5717,32 +5717,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127028741</v>
+        <v>127028737</v>
       </c>
       <c r="B52" t="n">
-        <v>98463</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5752,10 +5752,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>460325</v>
+        <v>460333</v>
       </c>
       <c r="R52" t="n">
-        <v>6990076</v>
+        <v>6990071</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5814,32 +5814,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028711</v>
+        <v>127028723</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460385</v>
+        <v>460357</v>
       </c>
       <c r="R53" t="n">
-        <v>6990183</v>
+        <v>6989952</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028723</v>
+        <v>127028695</v>
       </c>
       <c r="B54" t="n">
         <v>80117</v>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460357</v>
+        <v>460416</v>
       </c>
       <c r="R54" t="n">
-        <v>6989952</v>
+        <v>6990144</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6008,32 +6008,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127028695</v>
+        <v>127028711</v>
       </c>
       <c r="B55" t="n">
-        <v>80117</v>
+        <v>98442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460416</v>
+        <v>460385</v>
       </c>
       <c r="R55" t="n">
-        <v>6990144</v>
+        <v>6990183</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3869,32 +3869,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127028687</v>
+        <v>127028680</v>
       </c>
       <c r="B33" t="n">
-        <v>80117</v>
+        <v>98463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460422</v>
+        <v>460426</v>
       </c>
       <c r="R33" t="n">
-        <v>6990185</v>
+        <v>6990076</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3940,11 +3940,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3971,32 +3966,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127028680</v>
+        <v>127028687</v>
       </c>
       <c r="B34" t="n">
-        <v>98463</v>
+        <v>80117</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4006,10 +4001,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460426</v>
+        <v>460422</v>
       </c>
       <c r="R34" t="n">
-        <v>6990076</v>
+        <v>6990185</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4042,6 +4037,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3481,10 +3481,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028721</v>
+        <v>127028668</v>
       </c>
       <c r="B29" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460361</v>
+        <v>460442</v>
       </c>
       <c r="R29" t="n">
         <v>6990074</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028668</v>
+        <v>127028716</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460442</v>
+        <v>460382</v>
       </c>
       <c r="R30" t="n">
-        <v>6990074</v>
+        <v>6990158</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127028716</v>
+        <v>127028721</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460382</v>
+        <v>460361</v>
       </c>
       <c r="R31" t="n">
-        <v>6990158</v>
+        <v>6990074</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3775,7 +3775,7 @@
         <v>127028719</v>
       </c>
       <c r="B32" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,32 +3869,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127028680</v>
+        <v>127028687</v>
       </c>
       <c r="B33" t="n">
-        <v>98463</v>
+        <v>80117</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460426</v>
+        <v>460422</v>
       </c>
       <c r="R33" t="n">
-        <v>6990076</v>
+        <v>6990185</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3940,6 +3940,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3966,32 +3971,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127028687</v>
+        <v>127028680</v>
       </c>
       <c r="B34" t="n">
-        <v>80117</v>
+        <v>98464</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4001,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460422</v>
+        <v>460426</v>
       </c>
       <c r="R34" t="n">
-        <v>6990185</v>
+        <v>6990076</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4037,11 +4042,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4071,7 +4071,7 @@
         <v>127028702</v>
       </c>
       <c r="B35" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127028631</v>
+        <v>127028693</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460580</v>
+        <v>460419</v>
       </c>
       <c r="R37" t="n">
-        <v>6990166</v>
+        <v>6990129</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4359,32 +4359,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127028658</v>
+        <v>127028632</v>
       </c>
       <c r="B38" t="n">
-        <v>98463</v>
+        <v>80117</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460450</v>
+        <v>460580</v>
       </c>
       <c r="R38" t="n">
-        <v>6989987</v>
+        <v>6990068</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4456,32 +4456,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028700</v>
+        <v>127028631</v>
       </c>
       <c r="B39" t="n">
-        <v>98463</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460399</v>
+        <v>460580</v>
       </c>
       <c r="R39" t="n">
-        <v>6990025</v>
+        <v>6990166</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028693</v>
+        <v>127028658</v>
       </c>
       <c r="B40" t="n">
-        <v>80117</v>
+        <v>98464</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460419</v>
+        <v>460450</v>
       </c>
       <c r="R40" t="n">
-        <v>6990129</v>
+        <v>6989987</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028632</v>
+        <v>127028700</v>
       </c>
       <c r="B41" t="n">
-        <v>80117</v>
+        <v>98464</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460580</v>
+        <v>460399</v>
       </c>
       <c r="R41" t="n">
-        <v>6990068</v>
+        <v>6990025</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4750,7 +4750,7 @@
         <v>127028647</v>
       </c>
       <c r="B42" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>127028726</v>
       </c>
       <c r="B43" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>127028734</v>
       </c>
       <c r="B44" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028634</v>
+        <v>127028750</v>
       </c>
       <c r="B46" t="n">
-        <v>80117</v>
+        <v>80118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5146,21 +5146,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460576</v>
+        <v>460302</v>
       </c>
       <c r="R46" t="n">
-        <v>6990197</v>
+        <v>6990069</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028750</v>
+        <v>127028692</v>
       </c>
       <c r="B47" t="n">
-        <v>80118</v>
+        <v>98443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460302</v>
+        <v>460419</v>
       </c>
       <c r="R47" t="n">
-        <v>6990069</v>
+        <v>6990164</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5329,32 +5329,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028692</v>
+        <v>127028634</v>
       </c>
       <c r="B48" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460419</v>
+        <v>460576</v>
       </c>
       <c r="R48" t="n">
-        <v>6990164</v>
+        <v>6990197</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5429,7 +5429,7 @@
         <v>127028755</v>
       </c>
       <c r="B49" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>127028682</v>
       </c>
       <c r="B50" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>127028741</v>
       </c>
       <c r="B51" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>127028737</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028723</v>
+        <v>127028695</v>
       </c>
       <c r="B53" t="n">
         <v>80117</v>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460357</v>
+        <v>460416</v>
       </c>
       <c r="R53" t="n">
-        <v>6989952</v>
+        <v>6990144</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028695</v>
+        <v>127028723</v>
       </c>
       <c r="B54" t="n">
         <v>80117</v>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460416</v>
+        <v>460357</v>
       </c>
       <c r="R54" t="n">
-        <v>6990144</v>
+        <v>6989952</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6011,7 +6011,7 @@
         <v>127028711</v>
       </c>
       <c r="B55" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3481,7 +3481,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028668</v>
+        <v>127028716</v>
       </c>
       <c r="B29" t="n">
         <v>98443</v>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460442</v>
+        <v>460382</v>
       </c>
       <c r="R29" t="n">
-        <v>6990074</v>
+        <v>6990158</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3578,7 +3578,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028716</v>
+        <v>127028668</v>
       </c>
       <c r="B30" t="n">
         <v>98443</v>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460382</v>
+        <v>460442</v>
       </c>
       <c r="R30" t="n">
-        <v>6990158</v>
+        <v>6990074</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127028693</v>
+        <v>127028700</v>
       </c>
       <c r="B37" t="n">
-        <v>80117</v>
+        <v>98464</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460419</v>
+        <v>460399</v>
       </c>
       <c r="R37" t="n">
-        <v>6990129</v>
+        <v>6990025</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4359,7 +4359,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127028632</v>
+        <v>127028693</v>
       </c>
       <c r="B38" t="n">
         <v>80117</v>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460580</v>
+        <v>460419</v>
       </c>
       <c r="R38" t="n">
-        <v>6990068</v>
+        <v>6990129</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4456,32 +4456,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028631</v>
+        <v>127028632</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
         <v>460580</v>
       </c>
       <c r="R39" t="n">
-        <v>6990166</v>
+        <v>6990068</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028658</v>
+        <v>127028631</v>
       </c>
       <c r="B40" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460450</v>
+        <v>460580</v>
       </c>
       <c r="R40" t="n">
-        <v>6989987</v>
+        <v>6990166</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,7 +4650,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028700</v>
+        <v>127028658</v>
       </c>
       <c r="B41" t="n">
         <v>98464</v>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460399</v>
+        <v>460450</v>
       </c>
       <c r="R41" t="n">
-        <v>6990025</v>
+        <v>6989987</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127028647</v>
+        <v>127028726</v>
       </c>
       <c r="B42" t="n">
         <v>98464</v>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460528</v>
+        <v>460354</v>
       </c>
       <c r="R42" t="n">
-        <v>6990066</v>
+        <v>6989926</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4844,7 +4844,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127028726</v>
+        <v>127028647</v>
       </c>
       <c r="B43" t="n">
         <v>98464</v>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460354</v>
+        <v>460528</v>
       </c>
       <c r="R43" t="n">
-        <v>6989926</v>
+        <v>6990066</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028692</v>
+        <v>127028634</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460419</v>
+        <v>460576</v>
       </c>
       <c r="R47" t="n">
-        <v>6990164</v>
+        <v>6990197</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5329,32 +5329,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028634</v>
+        <v>127028692</v>
       </c>
       <c r="B48" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460576</v>
+        <v>460419</v>
       </c>
       <c r="R48" t="n">
-        <v>6990197</v>
+        <v>6990164</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5814,7 +5814,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028695</v>
+        <v>127028723</v>
       </c>
       <c r="B53" t="n">
         <v>80117</v>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460416</v>
+        <v>460357</v>
       </c>
       <c r="R53" t="n">
-        <v>6990144</v>
+        <v>6989952</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028723</v>
+        <v>127028695</v>
       </c>
       <c r="B54" t="n">
         <v>80117</v>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460357</v>
+        <v>460416</v>
       </c>
       <c r="R54" t="n">
-        <v>6989952</v>
+        <v>6990144</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -4262,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127028700</v>
+        <v>127028693</v>
       </c>
       <c r="B37" t="n">
-        <v>98464</v>
+        <v>80117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460399</v>
+        <v>460419</v>
       </c>
       <c r="R37" t="n">
-        <v>6990025</v>
+        <v>6990129</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4359,7 +4359,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127028693</v>
+        <v>127028632</v>
       </c>
       <c r="B38" t="n">
         <v>80117</v>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460419</v>
+        <v>460580</v>
       </c>
       <c r="R38" t="n">
-        <v>6990129</v>
+        <v>6990068</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4456,32 +4456,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028632</v>
+        <v>127028631</v>
       </c>
       <c r="B39" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
         <v>460580</v>
       </c>
       <c r="R39" t="n">
-        <v>6990068</v>
+        <v>6990166</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028631</v>
+        <v>127028700</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460580</v>
+        <v>460399</v>
       </c>
       <c r="R40" t="n">
-        <v>6990166</v>
+        <v>6990025</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -5135,10 +5135,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028750</v>
+        <v>127028634</v>
       </c>
       <c r="B46" t="n">
-        <v>80118</v>
+        <v>80117</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5146,21 +5146,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460302</v>
+        <v>460576</v>
       </c>
       <c r="R46" t="n">
-        <v>6990069</v>
+        <v>6990197</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028634</v>
+        <v>127028692</v>
       </c>
       <c r="B47" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460576</v>
+        <v>460419</v>
       </c>
       <c r="R47" t="n">
-        <v>6990197</v>
+        <v>6990164</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5329,32 +5329,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028692</v>
+        <v>127028750</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>80118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460419</v>
+        <v>460302</v>
       </c>
       <c r="R48" t="n">
-        <v>6990164</v>
+        <v>6990069</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3290,7 +3290,7 @@
         <v>127028746</v>
       </c>
       <c r="B27" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>127028704</v>
       </c>
       <c r="B28" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028716</v>
+        <v>127028668</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460382</v>
+        <v>460442</v>
       </c>
       <c r="R29" t="n">
-        <v>6990158</v>
+        <v>6990074</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028668</v>
+        <v>127028716</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460442</v>
+        <v>460382</v>
       </c>
       <c r="R30" t="n">
-        <v>6990074</v>
+        <v>6990158</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3678,7 +3678,7 @@
         <v>127028721</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>127028719</v>
       </c>
       <c r="B32" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>127028687</v>
       </c>
       <c r="B33" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>127028680</v>
       </c>
       <c r="B34" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>127028702</v>
       </c>
       <c r="B35" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>127028731</v>
       </c>
       <c r="B36" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>127028693</v>
       </c>
       <c r="B37" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>127028632</v>
       </c>
       <c r="B38" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4456,32 +4456,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028631</v>
+        <v>127028658</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>98468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460580</v>
+        <v>460450</v>
       </c>
       <c r="R39" t="n">
-        <v>6990166</v>
+        <v>6989987</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4556,7 +4556,7 @@
         <v>127028700</v>
       </c>
       <c r="B40" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028658</v>
+        <v>127028631</v>
       </c>
       <c r="B41" t="n">
-        <v>98464</v>
+        <v>98447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460450</v>
+        <v>460580</v>
       </c>
       <c r="R41" t="n">
-        <v>6989987</v>
+        <v>6990166</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4747,10 +4747,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127028726</v>
+        <v>127028647</v>
       </c>
       <c r="B42" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460354</v>
+        <v>460528</v>
       </c>
       <c r="R42" t="n">
-        <v>6989926</v>
+        <v>6990066</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127028647</v>
+        <v>127028726</v>
       </c>
       <c r="B43" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460528</v>
+        <v>460354</v>
       </c>
       <c r="R43" t="n">
-        <v>6990066</v>
+        <v>6989926</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4944,7 +4944,7 @@
         <v>127028734</v>
       </c>
       <c r="B44" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>127028626</v>
       </c>
       <c r="B45" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028634</v>
+        <v>127028750</v>
       </c>
       <c r="B46" t="n">
-        <v>80117</v>
+        <v>80122</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5146,21 +5146,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460576</v>
+        <v>460302</v>
       </c>
       <c r="R46" t="n">
-        <v>6990197</v>
+        <v>6990069</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028692</v>
+        <v>127028634</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>80121</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460419</v>
+        <v>460576</v>
       </c>
       <c r="R47" t="n">
-        <v>6990164</v>
+        <v>6990197</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5329,32 +5329,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028750</v>
+        <v>127028755</v>
       </c>
       <c r="B48" t="n">
-        <v>80118</v>
+        <v>98468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460302</v>
+        <v>460239</v>
       </c>
       <c r="R48" t="n">
-        <v>6990069</v>
+        <v>6990025</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5426,32 +5426,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127028755</v>
+        <v>127028692</v>
       </c>
       <c r="B49" t="n">
-        <v>98464</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460239</v>
+        <v>460419</v>
       </c>
       <c r="R49" t="n">
-        <v>6990025</v>
+        <v>6990164</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5526,7 +5526,7 @@
         <v>127028682</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>127028741</v>
       </c>
       <c r="B51" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>127028737</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028723</v>
+        <v>127028695</v>
       </c>
       <c r="B53" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460357</v>
+        <v>460416</v>
       </c>
       <c r="R53" t="n">
-        <v>6989952</v>
+        <v>6990144</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,10 +5911,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028695</v>
+        <v>127028723</v>
       </c>
       <c r="B54" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460416</v>
+        <v>460357</v>
       </c>
       <c r="R54" t="n">
-        <v>6990144</v>
+        <v>6989952</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6011,7 +6011,7 @@
         <v>127028711</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3869,32 +3869,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127028687</v>
+        <v>127028680</v>
       </c>
       <c r="B33" t="n">
-        <v>80121</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460422</v>
+        <v>460426</v>
       </c>
       <c r="R33" t="n">
-        <v>6990185</v>
+        <v>6990076</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3940,11 +3940,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3971,32 +3966,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127028680</v>
+        <v>127028687</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>80121</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4006,10 +4001,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460426</v>
+        <v>460422</v>
       </c>
       <c r="R34" t="n">
-        <v>6990076</v>
+        <v>6990185</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4042,6 +4037,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4262,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127028693</v>
+        <v>127028631</v>
       </c>
       <c r="B37" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460419</v>
+        <v>460580</v>
       </c>
       <c r="R37" t="n">
-        <v>6990129</v>
+        <v>6990166</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4359,32 +4359,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127028632</v>
+        <v>127028658</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>98468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460580</v>
+        <v>460450</v>
       </c>
       <c r="R38" t="n">
-        <v>6990068</v>
+        <v>6989987</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4456,7 +4456,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028658</v>
+        <v>127028700</v>
       </c>
       <c r="B39" t="n">
         <v>98468</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460450</v>
+        <v>460399</v>
       </c>
       <c r="R39" t="n">
-        <v>6989987</v>
+        <v>6990025</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028700</v>
+        <v>127028693</v>
       </c>
       <c r="B40" t="n">
-        <v>98468</v>
+        <v>80121</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460399</v>
+        <v>460419</v>
       </c>
       <c r="R40" t="n">
-        <v>6990025</v>
+        <v>6990129</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028631</v>
+        <v>127028632</v>
       </c>
       <c r="B41" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,7 +4688,7 @@
         <v>460580</v>
       </c>
       <c r="R41" t="n">
-        <v>6990166</v>
+        <v>6990068</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028634</v>
+        <v>127028692</v>
       </c>
       <c r="B47" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460576</v>
+        <v>460419</v>
       </c>
       <c r="R47" t="n">
-        <v>6990197</v>
+        <v>6990164</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5426,32 +5426,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127028692</v>
+        <v>127028634</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460419</v>
+        <v>460576</v>
       </c>
       <c r="R49" t="n">
-        <v>6990164</v>
+        <v>6990197</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5620,32 +5620,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127028741</v>
+        <v>127028737</v>
       </c>
       <c r="B51" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>460325</v>
+        <v>460333</v>
       </c>
       <c r="R51" t="n">
-        <v>6990076</v>
+        <v>6990071</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5717,32 +5717,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127028737</v>
+        <v>127028741</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>98468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5752,10 +5752,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>460333</v>
+        <v>460325</v>
       </c>
       <c r="R52" t="n">
-        <v>6990071</v>
+        <v>6990076</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5814,7 +5814,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028695</v>
+        <v>127028723</v>
       </c>
       <c r="B53" t="n">
         <v>80121</v>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460416</v>
+        <v>460357</v>
       </c>
       <c r="R53" t="n">
-        <v>6990144</v>
+        <v>6989952</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028723</v>
+        <v>127028695</v>
       </c>
       <c r="B54" t="n">
         <v>80121</v>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460357</v>
+        <v>460416</v>
       </c>
       <c r="R54" t="n">
-        <v>6989952</v>
+        <v>6990144</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3869,32 +3869,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127028680</v>
+        <v>127028687</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>80121</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460426</v>
+        <v>460422</v>
       </c>
       <c r="R33" t="n">
-        <v>6990076</v>
+        <v>6990185</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3940,6 +3940,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3966,32 +3971,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127028687</v>
+        <v>127028680</v>
       </c>
       <c r="B34" t="n">
-        <v>80121</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4001,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460422</v>
+        <v>460426</v>
       </c>
       <c r="R34" t="n">
-        <v>6990185</v>
+        <v>6990076</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4037,11 +4042,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5135,10 +5135,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028750</v>
+        <v>127028634</v>
       </c>
       <c r="B46" t="n">
-        <v>80122</v>
+        <v>80121</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5146,21 +5146,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460302</v>
+        <v>460576</v>
       </c>
       <c r="R46" t="n">
-        <v>6990069</v>
+        <v>6990197</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028692</v>
+        <v>127028750</v>
       </c>
       <c r="B47" t="n">
-        <v>98447</v>
+        <v>80122</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460419</v>
+        <v>460302</v>
       </c>
       <c r="R47" t="n">
-        <v>6990164</v>
+        <v>6990069</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5329,32 +5329,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028755</v>
+        <v>127028692</v>
       </c>
       <c r="B48" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460239</v>
+        <v>460419</v>
       </c>
       <c r="R48" t="n">
-        <v>6990025</v>
+        <v>6990164</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5426,32 +5426,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127028634</v>
+        <v>127028755</v>
       </c>
       <c r="B49" t="n">
-        <v>80121</v>
+        <v>98468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460576</v>
+        <v>460239</v>
       </c>
       <c r="R49" t="n">
-        <v>6990197</v>
+        <v>6990025</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5814,32 +5814,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028723</v>
+        <v>127028711</v>
       </c>
       <c r="B53" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460357</v>
+        <v>460385</v>
       </c>
       <c r="R53" t="n">
-        <v>6989952</v>
+        <v>6990183</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028695</v>
+        <v>127028723</v>
       </c>
       <c r="B54" t="n">
         <v>80121</v>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460416</v>
+        <v>460357</v>
       </c>
       <c r="R54" t="n">
-        <v>6990144</v>
+        <v>6989952</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6008,32 +6008,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127028711</v>
+        <v>127028695</v>
       </c>
       <c r="B55" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460385</v>
+        <v>460416</v>
       </c>
       <c r="R55" t="n">
-        <v>6990183</v>
+        <v>6990144</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3869,32 +3869,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127028687</v>
+        <v>127028680</v>
       </c>
       <c r="B33" t="n">
-        <v>80121</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460422</v>
+        <v>460426</v>
       </c>
       <c r="R33" t="n">
-        <v>6990185</v>
+        <v>6990076</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3940,11 +3940,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3971,32 +3966,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127028680</v>
+        <v>127028687</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>80121</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4006,10 +4001,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460426</v>
+        <v>460422</v>
       </c>
       <c r="R34" t="n">
-        <v>6990076</v>
+        <v>6990185</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4042,6 +4037,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4262,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127028631</v>
+        <v>127028693</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460580</v>
+        <v>460419</v>
       </c>
       <c r="R37" t="n">
-        <v>6990166</v>
+        <v>6990129</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4359,32 +4359,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127028658</v>
+        <v>127028632</v>
       </c>
       <c r="B38" t="n">
-        <v>98468</v>
+        <v>80121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460450</v>
+        <v>460580</v>
       </c>
       <c r="R38" t="n">
-        <v>6989987</v>
+        <v>6990068</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4456,32 +4456,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028700</v>
+        <v>127028631</v>
       </c>
       <c r="B39" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460399</v>
+        <v>460580</v>
       </c>
       <c r="R39" t="n">
-        <v>6990025</v>
+        <v>6990166</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028693</v>
+        <v>127028658</v>
       </c>
       <c r="B40" t="n">
-        <v>80121</v>
+        <v>98468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460419</v>
+        <v>460450</v>
       </c>
       <c r="R40" t="n">
-        <v>6990129</v>
+        <v>6989987</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028632</v>
+        <v>127028700</v>
       </c>
       <c r="B41" t="n">
-        <v>80121</v>
+        <v>98468</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460580</v>
+        <v>460399</v>
       </c>
       <c r="R41" t="n">
-        <v>6990068</v>
+        <v>6990025</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028634</v>
+        <v>127028750</v>
       </c>
       <c r="B46" t="n">
-        <v>80121</v>
+        <v>80122</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5146,21 +5146,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460576</v>
+        <v>460302</v>
       </c>
       <c r="R46" t="n">
-        <v>6990197</v>
+        <v>6990069</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028750</v>
+        <v>127028692</v>
       </c>
       <c r="B47" t="n">
-        <v>80122</v>
+        <v>98447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460302</v>
+        <v>460419</v>
       </c>
       <c r="R47" t="n">
-        <v>6990069</v>
+        <v>6990164</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5329,32 +5329,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028692</v>
+        <v>127028755</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>98468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460419</v>
+        <v>460239</v>
       </c>
       <c r="R48" t="n">
-        <v>6990164</v>
+        <v>6990025</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5426,32 +5426,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127028755</v>
+        <v>127028634</v>
       </c>
       <c r="B49" t="n">
-        <v>98468</v>
+        <v>80121</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460239</v>
+        <v>460576</v>
       </c>
       <c r="R49" t="n">
-        <v>6990025</v>
+        <v>6990197</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5814,32 +5814,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028711</v>
+        <v>127028723</v>
       </c>
       <c r="B53" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460385</v>
+        <v>460357</v>
       </c>
       <c r="R53" t="n">
-        <v>6990183</v>
+        <v>6989952</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028723</v>
+        <v>127028695</v>
       </c>
       <c r="B54" t="n">
         <v>80121</v>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460357</v>
+        <v>460416</v>
       </c>
       <c r="R54" t="n">
-        <v>6989952</v>
+        <v>6990144</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6008,32 +6008,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127028695</v>
+        <v>127028711</v>
       </c>
       <c r="B55" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460416</v>
+        <v>460385</v>
       </c>
       <c r="R55" t="n">
-        <v>6990144</v>
+        <v>6990183</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3481,10 +3481,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028668</v>
+        <v>127028716</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460442</v>
+        <v>460382</v>
       </c>
       <c r="R29" t="n">
-        <v>6990074</v>
+        <v>6990158</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028716</v>
+        <v>127028721</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460382</v>
+        <v>460361</v>
       </c>
       <c r="R30" t="n">
-        <v>6990158</v>
+        <v>6990074</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127028721</v>
+        <v>127028668</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460361</v>
+        <v>460442</v>
       </c>
       <c r="R31" t="n">
         <v>6990074</v>
@@ -3775,7 +3775,7 @@
         <v>127028719</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,32 +3869,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127028680</v>
+        <v>127028687</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>80121</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460426</v>
+        <v>460422</v>
       </c>
       <c r="R33" t="n">
-        <v>6990076</v>
+        <v>6990185</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3940,6 +3940,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3966,32 +3971,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127028687</v>
+        <v>127028680</v>
       </c>
       <c r="B34" t="n">
-        <v>80121</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4001,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460422</v>
+        <v>460426</v>
       </c>
       <c r="R34" t="n">
-        <v>6990185</v>
+        <v>6990076</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4037,11 +4042,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4071,7 +4071,7 @@
         <v>127028702</v>
       </c>
       <c r="B35" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,32 +4456,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028631</v>
+        <v>127028658</v>
       </c>
       <c r="B39" t="n">
-        <v>98447</v>
+        <v>98469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460580</v>
+        <v>460450</v>
       </c>
       <c r="R39" t="n">
-        <v>6990166</v>
+        <v>6989987</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028658</v>
+        <v>127028700</v>
       </c>
       <c r="B40" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460450</v>
+        <v>460399</v>
       </c>
       <c r="R40" t="n">
-        <v>6989987</v>
+        <v>6990025</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028700</v>
+        <v>127028631</v>
       </c>
       <c r="B41" t="n">
-        <v>98468</v>
+        <v>98448</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460399</v>
+        <v>460580</v>
       </c>
       <c r="R41" t="n">
-        <v>6990025</v>
+        <v>6990166</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4750,7 +4750,7 @@
         <v>127028647</v>
       </c>
       <c r="B42" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>127028726</v>
       </c>
       <c r="B43" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>127028734</v>
       </c>
       <c r="B44" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028750</v>
+        <v>127028634</v>
       </c>
       <c r="B46" t="n">
-        <v>80122</v>
+        <v>80121</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5146,21 +5146,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460302</v>
+        <v>460576</v>
       </c>
       <c r="R46" t="n">
-        <v>6990069</v>
+        <v>6990197</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028692</v>
+        <v>127028750</v>
       </c>
       <c r="B47" t="n">
-        <v>98447</v>
+        <v>80122</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460419</v>
+        <v>460302</v>
       </c>
       <c r="R47" t="n">
-        <v>6990164</v>
+        <v>6990069</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5329,32 +5329,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028755</v>
+        <v>127028692</v>
       </c>
       <c r="B48" t="n">
-        <v>98468</v>
+        <v>98448</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460239</v>
+        <v>460419</v>
       </c>
       <c r="R48" t="n">
-        <v>6990025</v>
+        <v>6990164</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5426,32 +5426,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127028634</v>
+        <v>127028755</v>
       </c>
       <c r="B49" t="n">
-        <v>80121</v>
+        <v>98469</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460576</v>
+        <v>460239</v>
       </c>
       <c r="R49" t="n">
-        <v>6990197</v>
+        <v>6990025</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5526,7 +5526,7 @@
         <v>127028682</v>
       </c>
       <c r="B50" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>127028737</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>127028741</v>
       </c>
       <c r="B52" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>127028711</v>
       </c>
       <c r="B55" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -5814,32 +5814,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028723</v>
+        <v>127028711</v>
       </c>
       <c r="B53" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460357</v>
+        <v>460385</v>
       </c>
       <c r="R53" t="n">
-        <v>6989952</v>
+        <v>6990183</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028695</v>
+        <v>127028723</v>
       </c>
       <c r="B54" t="n">
         <v>80121</v>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460416</v>
+        <v>460357</v>
       </c>
       <c r="R54" t="n">
-        <v>6990144</v>
+        <v>6989952</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6008,32 +6008,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127028711</v>
+        <v>127028695</v>
       </c>
       <c r="B55" t="n">
-        <v>98448</v>
+        <v>80121</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460385</v>
+        <v>460416</v>
       </c>
       <c r="R55" t="n">
-        <v>6990183</v>
+        <v>6990144</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3290,7 +3290,7 @@
         <v>127028746</v>
       </c>
       <c r="B27" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>127028704</v>
       </c>
       <c r="B28" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028716</v>
+        <v>127028668</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460382</v>
+        <v>460442</v>
       </c>
       <c r="R29" t="n">
-        <v>6990158</v>
+        <v>6990074</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028721</v>
+        <v>127028716</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460361</v>
+        <v>460382</v>
       </c>
       <c r="R30" t="n">
-        <v>6990074</v>
+        <v>6990158</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127028668</v>
+        <v>127028721</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460442</v>
+        <v>460361</v>
       </c>
       <c r="R31" t="n">
         <v>6990074</v>
@@ -3775,7 +3775,7 @@
         <v>127028719</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>127028687</v>
       </c>
       <c r="B33" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>127028680</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>127028702</v>
       </c>
       <c r="B35" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>127028731</v>
       </c>
       <c r="B36" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127028693</v>
+        <v>127028631</v>
       </c>
       <c r="B37" t="n">
-        <v>80121</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460419</v>
+        <v>460580</v>
       </c>
       <c r="R37" t="n">
-        <v>6990129</v>
+        <v>6990166</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4359,32 +4359,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127028632</v>
+        <v>127028700</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>98471</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460580</v>
+        <v>460399</v>
       </c>
       <c r="R38" t="n">
-        <v>6990068</v>
+        <v>6990025</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4459,7 +4459,7 @@
         <v>127028658</v>
       </c>
       <c r="B39" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028700</v>
+        <v>127028693</v>
       </c>
       <c r="B40" t="n">
-        <v>98469</v>
+        <v>80123</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460399</v>
+        <v>460419</v>
       </c>
       <c r="R40" t="n">
-        <v>6990025</v>
+        <v>6990129</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028631</v>
+        <v>127028632</v>
       </c>
       <c r="B41" t="n">
-        <v>98448</v>
+        <v>80123</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,7 +4688,7 @@
         <v>460580</v>
       </c>
       <c r="R41" t="n">
-        <v>6990166</v>
+        <v>6990068</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4747,10 +4747,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127028647</v>
+        <v>127028726</v>
       </c>
       <c r="B42" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460528</v>
+        <v>460354</v>
       </c>
       <c r="R42" t="n">
-        <v>6990066</v>
+        <v>6989926</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127028726</v>
+        <v>127028647</v>
       </c>
       <c r="B43" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460354</v>
+        <v>460528</v>
       </c>
       <c r="R43" t="n">
-        <v>6989926</v>
+        <v>6990066</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4944,7 +4944,7 @@
         <v>127028734</v>
       </c>
       <c r="B44" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>127028626</v>
       </c>
       <c r="B45" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028634</v>
+        <v>127028750</v>
       </c>
       <c r="B46" t="n">
-        <v>80121</v>
+        <v>80124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5146,21 +5146,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460576</v>
+        <v>460302</v>
       </c>
       <c r="R46" t="n">
-        <v>6990197</v>
+        <v>6990069</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028750</v>
+        <v>127028634</v>
       </c>
       <c r="B47" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460302</v>
+        <v>460576</v>
       </c>
       <c r="R47" t="n">
-        <v>6990069</v>
+        <v>6990197</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5332,7 +5332,7 @@
         <v>127028692</v>
       </c>
       <c r="B48" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>127028755</v>
       </c>
       <c r="B49" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>127028682</v>
       </c>
       <c r="B50" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>127028737</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>127028741</v>
       </c>
       <c r="B52" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5814,32 +5814,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028711</v>
+        <v>127028723</v>
       </c>
       <c r="B53" t="n">
-        <v>98448</v>
+        <v>80123</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460385</v>
+        <v>460357</v>
       </c>
       <c r="R53" t="n">
-        <v>6990183</v>
+        <v>6989952</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,10 +5911,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028723</v>
+        <v>127028695</v>
       </c>
       <c r="B54" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460357</v>
+        <v>460416</v>
       </c>
       <c r="R54" t="n">
-        <v>6989952</v>
+        <v>6990144</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6008,32 +6008,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127028695</v>
+        <v>127028711</v>
       </c>
       <c r="B55" t="n">
-        <v>80121</v>
+        <v>98450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460416</v>
+        <v>460385</v>
       </c>
       <c r="R55" t="n">
-        <v>6990144</v>
+        <v>6990183</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -4262,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127028631</v>
+        <v>127028693</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460580</v>
+        <v>460419</v>
       </c>
       <c r="R37" t="n">
-        <v>6990166</v>
+        <v>6990129</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4359,32 +4359,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127028700</v>
+        <v>127028632</v>
       </c>
       <c r="B38" t="n">
-        <v>98471</v>
+        <v>80123</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460399</v>
+        <v>460580</v>
       </c>
       <c r="R38" t="n">
-        <v>6990025</v>
+        <v>6990068</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028693</v>
+        <v>127028700</v>
       </c>
       <c r="B40" t="n">
-        <v>80123</v>
+        <v>98471</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460419</v>
+        <v>460399</v>
       </c>
       <c r="R40" t="n">
-        <v>6990129</v>
+        <v>6990025</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028632</v>
+        <v>127028631</v>
       </c>
       <c r="B41" t="n">
-        <v>80123</v>
+        <v>98450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,7 +4688,7 @@
         <v>460580</v>
       </c>
       <c r="R41" t="n">
-        <v>6990068</v>
+        <v>6990166</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127028726</v>
+        <v>127028647</v>
       </c>
       <c r="B42" t="n">
         <v>98471</v>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460354</v>
+        <v>460528</v>
       </c>
       <c r="R42" t="n">
-        <v>6989926</v>
+        <v>6990066</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4844,7 +4844,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127028647</v>
+        <v>127028726</v>
       </c>
       <c r="B43" t="n">
         <v>98471</v>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460528</v>
+        <v>460354</v>
       </c>
       <c r="R43" t="n">
-        <v>6990066</v>
+        <v>6989926</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5329,32 +5329,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028692</v>
+        <v>127028755</v>
       </c>
       <c r="B48" t="n">
-        <v>98450</v>
+        <v>98471</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460419</v>
+        <v>460239</v>
       </c>
       <c r="R48" t="n">
-        <v>6990164</v>
+        <v>6990025</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5426,32 +5426,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127028755</v>
+        <v>127028692</v>
       </c>
       <c r="B49" t="n">
-        <v>98471</v>
+        <v>98450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460239</v>
+        <v>460419</v>
       </c>
       <c r="R49" t="n">
-        <v>6990025</v>
+        <v>6990164</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5620,32 +5620,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127028737</v>
+        <v>127028741</v>
       </c>
       <c r="B51" t="n">
-        <v>98450</v>
+        <v>98471</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>460333</v>
+        <v>460325</v>
       </c>
       <c r="R51" t="n">
-        <v>6990071</v>
+        <v>6990076</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5717,32 +5717,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127028741</v>
+        <v>127028737</v>
       </c>
       <c r="B52" t="n">
-        <v>98471</v>
+        <v>98450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5752,10 +5752,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>460325</v>
+        <v>460333</v>
       </c>
       <c r="R52" t="n">
-        <v>6990076</v>
+        <v>6990071</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3869,32 +3869,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127028687</v>
+        <v>127028680</v>
       </c>
       <c r="B33" t="n">
-        <v>80123</v>
+        <v>98471</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460422</v>
+        <v>460426</v>
       </c>
       <c r="R33" t="n">
-        <v>6990185</v>
+        <v>6990076</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3940,11 +3940,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3971,32 +3966,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127028680</v>
+        <v>127028687</v>
       </c>
       <c r="B34" t="n">
-        <v>98471</v>
+        <v>80123</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4006,10 +4001,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460426</v>
+        <v>460422</v>
       </c>
       <c r="R34" t="n">
-        <v>6990076</v>
+        <v>6990185</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4042,6 +4037,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5135,10 +5135,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028750</v>
+        <v>127028634</v>
       </c>
       <c r="B46" t="n">
-        <v>80124</v>
+        <v>80123</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5146,21 +5146,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460302</v>
+        <v>460576</v>
       </c>
       <c r="R46" t="n">
-        <v>6990069</v>
+        <v>6990197</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028634</v>
+        <v>127028750</v>
       </c>
       <c r="B47" t="n">
-        <v>80123</v>
+        <v>80124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460576</v>
+        <v>460302</v>
       </c>
       <c r="R47" t="n">
-        <v>6990197</v>
+        <v>6990069</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3481,10 +3481,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028668</v>
+        <v>127028716</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460442</v>
+        <v>460382</v>
       </c>
       <c r="R29" t="n">
-        <v>6990074</v>
+        <v>6990158</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028716</v>
+        <v>127028668</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460382</v>
+        <v>460442</v>
       </c>
       <c r="R30" t="n">
-        <v>6990158</v>
+        <v>6990074</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3678,7 +3678,7 @@
         <v>127028721</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>127028719</v>
       </c>
       <c r="B32" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,32 +3869,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127028680</v>
+        <v>127028687</v>
       </c>
       <c r="B33" t="n">
-        <v>98471</v>
+        <v>80123</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460426</v>
+        <v>460422</v>
       </c>
       <c r="R33" t="n">
-        <v>6990076</v>
+        <v>6990185</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3940,6 +3940,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3966,32 +3971,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127028687</v>
+        <v>127028680</v>
       </c>
       <c r="B34" t="n">
-        <v>80123</v>
+        <v>98477</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4001,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460422</v>
+        <v>460426</v>
       </c>
       <c r="R34" t="n">
-        <v>6990185</v>
+        <v>6990076</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4037,11 +4042,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4071,7 +4071,7 @@
         <v>127028702</v>
       </c>
       <c r="B35" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,32 +4456,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028658</v>
+        <v>127028631</v>
       </c>
       <c r="B39" t="n">
-        <v>98471</v>
+        <v>98456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460450</v>
+        <v>460580</v>
       </c>
       <c r="R39" t="n">
-        <v>6989987</v>
+        <v>6990166</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028700</v>
+        <v>127028658</v>
       </c>
       <c r="B40" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460399</v>
+        <v>460450</v>
       </c>
       <c r="R40" t="n">
-        <v>6990025</v>
+        <v>6989987</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028631</v>
+        <v>127028700</v>
       </c>
       <c r="B41" t="n">
-        <v>98450</v>
+        <v>98477</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460580</v>
+        <v>460399</v>
       </c>
       <c r="R41" t="n">
-        <v>6990166</v>
+        <v>6990025</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4750,7 +4750,7 @@
         <v>127028647</v>
       </c>
       <c r="B42" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>127028726</v>
       </c>
       <c r="B43" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>127028734</v>
       </c>
       <c r="B44" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5135,32 +5135,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028634</v>
+        <v>127028755</v>
       </c>
       <c r="B46" t="n">
-        <v>80123</v>
+        <v>98477</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460576</v>
+        <v>460239</v>
       </c>
       <c r="R46" t="n">
-        <v>6990197</v>
+        <v>6990025</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028750</v>
+        <v>127028692</v>
       </c>
       <c r="B47" t="n">
-        <v>80124</v>
+        <v>98456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460302</v>
+        <v>460419</v>
       </c>
       <c r="R47" t="n">
-        <v>6990069</v>
+        <v>6990164</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5329,32 +5329,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028755</v>
+        <v>127028750</v>
       </c>
       <c r="B48" t="n">
-        <v>98471</v>
+        <v>80124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460239</v>
+        <v>460302</v>
       </c>
       <c r="R48" t="n">
-        <v>6990025</v>
+        <v>6990069</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5426,32 +5426,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127028692</v>
+        <v>127028634</v>
       </c>
       <c r="B49" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460419</v>
+        <v>460576</v>
       </c>
       <c r="R49" t="n">
-        <v>6990164</v>
+        <v>6990197</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5526,7 +5526,7 @@
         <v>127028682</v>
       </c>
       <c r="B50" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5620,32 +5620,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127028741</v>
+        <v>127028737</v>
       </c>
       <c r="B51" t="n">
-        <v>98471</v>
+        <v>98456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>460325</v>
+        <v>460333</v>
       </c>
       <c r="R51" t="n">
-        <v>6990076</v>
+        <v>6990071</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5717,32 +5717,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127028737</v>
+        <v>127028741</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>98477</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5752,10 +5752,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>460333</v>
+        <v>460325</v>
       </c>
       <c r="R52" t="n">
-        <v>6990071</v>
+        <v>6990076</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5814,32 +5814,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028723</v>
+        <v>127028711</v>
       </c>
       <c r="B53" t="n">
-        <v>80123</v>
+        <v>98456</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460357</v>
+        <v>460385</v>
       </c>
       <c r="R53" t="n">
-        <v>6989952</v>
+        <v>6990183</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028695</v>
+        <v>127028723</v>
       </c>
       <c r="B54" t="n">
         <v>80123</v>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460416</v>
+        <v>460357</v>
       </c>
       <c r="R54" t="n">
-        <v>6990144</v>
+        <v>6989952</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6008,32 +6008,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127028711</v>
+        <v>127028695</v>
       </c>
       <c r="B55" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460385</v>
+        <v>460416</v>
       </c>
       <c r="R55" t="n">
-        <v>6990183</v>
+        <v>6990144</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -3290,7 +3290,7 @@
         <v>127028746</v>
       </c>
       <c r="B27" t="n">
-        <v>80124</v>
+        <v>80115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>127028704</v>
       </c>
       <c r="B28" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028716</v>
+        <v>127028668</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460382</v>
+        <v>460442</v>
       </c>
       <c r="R29" t="n">
-        <v>6990158</v>
+        <v>6990074</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028668</v>
+        <v>127028716</v>
       </c>
       <c r="B30" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460442</v>
+        <v>460382</v>
       </c>
       <c r="R30" t="n">
-        <v>6990074</v>
+        <v>6990158</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3678,7 +3678,7 @@
         <v>127028721</v>
       </c>
       <c r="B31" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>127028719</v>
       </c>
       <c r="B32" t="n">
-        <v>98477</v>
+        <v>98457</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>127028687</v>
       </c>
       <c r="B33" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>127028680</v>
       </c>
       <c r="B34" t="n">
-        <v>98477</v>
+        <v>98457</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>127028702</v>
       </c>
       <c r="B35" t="n">
-        <v>98477</v>
+        <v>98457</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>127028731</v>
       </c>
       <c r="B36" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4262,32 +4262,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127028693</v>
+        <v>127028631</v>
       </c>
       <c r="B37" t="n">
-        <v>80123</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460419</v>
+        <v>460580</v>
       </c>
       <c r="R37" t="n">
-        <v>6990129</v>
+        <v>6990166</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4359,32 +4359,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127028632</v>
+        <v>127028700</v>
       </c>
       <c r="B38" t="n">
-        <v>80123</v>
+        <v>98457</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460580</v>
+        <v>460399</v>
       </c>
       <c r="R38" t="n">
-        <v>6990068</v>
+        <v>6990025</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4456,32 +4456,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028631</v>
+        <v>127028658</v>
       </c>
       <c r="B39" t="n">
-        <v>98456</v>
+        <v>98457</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460580</v>
+        <v>460450</v>
       </c>
       <c r="R39" t="n">
-        <v>6990166</v>
+        <v>6989987</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4553,32 +4553,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028658</v>
+        <v>127028693</v>
       </c>
       <c r="B40" t="n">
-        <v>98477</v>
+        <v>80114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460450</v>
+        <v>460419</v>
       </c>
       <c r="R40" t="n">
-        <v>6989987</v>
+        <v>6990129</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4650,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028700</v>
+        <v>127028632</v>
       </c>
       <c r="B41" t="n">
-        <v>98477</v>
+        <v>80114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460399</v>
+        <v>460580</v>
       </c>
       <c r="R41" t="n">
-        <v>6990025</v>
+        <v>6990068</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4747,10 +4747,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127028647</v>
+        <v>127028726</v>
       </c>
       <c r="B42" t="n">
-        <v>98477</v>
+        <v>98457</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460528</v>
+        <v>460354</v>
       </c>
       <c r="R42" t="n">
-        <v>6990066</v>
+        <v>6989926</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127028726</v>
+        <v>127028647</v>
       </c>
       <c r="B43" t="n">
-        <v>98477</v>
+        <v>98457</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460354</v>
+        <v>460528</v>
       </c>
       <c r="R43" t="n">
-        <v>6989926</v>
+        <v>6990066</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4944,7 +4944,7 @@
         <v>127028734</v>
       </c>
       <c r="B44" t="n">
-        <v>98477</v>
+        <v>98457</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>127028626</v>
       </c>
       <c r="B45" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5135,32 +5135,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028755</v>
+        <v>127028692</v>
       </c>
       <c r="B46" t="n">
-        <v>98477</v>
+        <v>98436</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460239</v>
+        <v>460419</v>
       </c>
       <c r="R46" t="n">
-        <v>6990025</v>
+        <v>6990164</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028692</v>
+        <v>127028755</v>
       </c>
       <c r="B47" t="n">
-        <v>98456</v>
+        <v>98457</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460419</v>
+        <v>460239</v>
       </c>
       <c r="R47" t="n">
-        <v>6990164</v>
+        <v>6990025</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5332,7 +5332,7 @@
         <v>127028750</v>
       </c>
       <c r="B48" t="n">
-        <v>80124</v>
+        <v>80115</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>127028634</v>
       </c>
       <c r="B49" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>127028682</v>
       </c>
       <c r="B50" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>127028737</v>
       </c>
       <c r="B51" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>127028741</v>
       </c>
       <c r="B52" t="n">
-        <v>98477</v>
+        <v>98457</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5814,32 +5814,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028711</v>
+        <v>127028723</v>
       </c>
       <c r="B53" t="n">
-        <v>98456</v>
+        <v>80114</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460385</v>
+        <v>460357</v>
       </c>
       <c r="R53" t="n">
-        <v>6990183</v>
+        <v>6989952</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5911,10 +5911,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028723</v>
+        <v>127028695</v>
       </c>
       <c r="B54" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460357</v>
+        <v>460416</v>
       </c>
       <c r="R54" t="n">
-        <v>6989952</v>
+        <v>6990144</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6008,32 +6008,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127028695</v>
+        <v>127028711</v>
       </c>
       <c r="B55" t="n">
-        <v>80123</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460416</v>
+        <v>460385</v>
       </c>
       <c r="R55" t="n">
-        <v>6990144</v>
+        <v>6990183</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>

--- a/artfynd/A 32037-2025 artfynd.xlsx
+++ b/artfynd/A 32037-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114577031</v>
+        <v>114578241</v>
       </c>
       <c r="B2" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460571</v>
+        <v>460437</v>
       </c>
       <c r="R2" t="n">
-        <v>6989896</v>
+        <v>6989899</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,53 +772,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114577030</v>
+        <v>126287535</v>
       </c>
       <c r="B3" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460481</v>
+        <v>460539</v>
       </c>
       <c r="R3" t="n">
-        <v>6989926</v>
+        <v>6989868</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +840,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,33 +869,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114578241</v>
+        <v>127028746</v>
       </c>
       <c r="B4" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +899,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460437</v>
+        <v>460314</v>
       </c>
       <c r="R4" t="n">
-        <v>6989899</v>
+        <v>6990069</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,65 +973,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114577029</v>
+        <v>127028750</v>
       </c>
       <c r="B5" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460379</v>
+        <v>460302</v>
       </c>
       <c r="R5" t="n">
-        <v>6989787</v>
+        <v>6990069</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,49 +1070,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114577084</v>
+        <v>114575544</v>
       </c>
       <c r="B6" t="n">
-        <v>97558</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219788</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460348</v>
+        <v>460486</v>
       </c>
       <c r="R6" t="n">
-        <v>6989896</v>
+        <v>6989924</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1179,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114576970</v>
+        <v>114575545</v>
       </c>
       <c r="B7" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460431</v>
+        <v>460513</v>
       </c>
       <c r="R7" t="n">
-        <v>6990169</v>
+        <v>6989938</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114577495</v>
+        <v>114575546</v>
       </c>
       <c r="B8" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460520</v>
+        <v>460547</v>
       </c>
       <c r="R8" t="n">
-        <v>6990168</v>
+        <v>6989916</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,19 +1373,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114575544</v>
+        <v>126287420</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1423,19 +1402,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460486</v>
+        <v>460597</v>
       </c>
       <c r="R9" t="n">
-        <v>6989924</v>
+        <v>6989850</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1441,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1473,71 +1470,67 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114578386</v>
+        <v>127028745</v>
       </c>
       <c r="B10" t="n">
-        <v>97671</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460534</v>
+        <v>460314</v>
       </c>
       <c r="R10" t="n">
-        <v>6990169</v>
+        <v>6990144</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1554,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,65 +1574,63 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114578349</v>
+        <v>126287460</v>
       </c>
       <c r="B11" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460391</v>
+        <v>460522</v>
       </c>
       <c r="R11" t="n">
-        <v>6990175</v>
+        <v>6989883</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,12 +1654,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,71 +1683,67 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114577528</v>
+        <v>127028626</v>
       </c>
       <c r="B12" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460355</v>
+        <v>460596</v>
       </c>
       <c r="R12" t="n">
-        <v>6989828</v>
+        <v>6990129</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1765,12 +1767,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,65 +1787,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114578387</v>
+        <v>127028632</v>
       </c>
       <c r="B13" t="n">
-        <v>97671</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460507</v>
+        <v>460580</v>
       </c>
       <c r="R13" t="n">
-        <v>6990170</v>
+        <v>6990068</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1867,12 +1864,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,27 +1884,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114575546</v>
+        <v>127028634</v>
       </c>
       <c r="B14" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,37 +1907,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460547</v>
+        <v>460576</v>
       </c>
       <c r="R14" t="n">
-        <v>6989916</v>
+        <v>6990197</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1969,12 +1961,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1989,65 +1981,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114578001</v>
+        <v>127028687</v>
       </c>
       <c r="B15" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460484</v>
+        <v>460422</v>
       </c>
       <c r="R15" t="n">
-        <v>6990176</v>
+        <v>6990185</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2071,12 +2058,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,65 +2083,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114576968</v>
+        <v>127028693</v>
       </c>
       <c r="B16" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460528</v>
+        <v>460419</v>
       </c>
       <c r="R16" t="n">
-        <v>6990169</v>
+        <v>6990129</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2173,12 +2160,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,65 +2180,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114578388</v>
+        <v>127028695</v>
       </c>
       <c r="B17" t="n">
-        <v>97671</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460434</v>
+        <v>460416</v>
       </c>
       <c r="R17" t="n">
-        <v>6990169</v>
+        <v>6990144</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2275,12 +2257,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2295,65 +2277,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114576971</v>
+        <v>127028704</v>
       </c>
       <c r="B18" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
         <v>460394</v>
       </c>
       <c r="R18" t="n">
-        <v>6990175</v>
+        <v>6990069</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2377,12 +2354,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2397,27 +2374,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114575545</v>
+        <v>127028723</v>
       </c>
       <c r="B19" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2397,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460513</v>
+        <v>460357</v>
       </c>
       <c r="R19" t="n">
-        <v>6989938</v>
+        <v>6989952</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2479,12 +2451,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2499,65 +2471,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114577496</v>
+        <v>127028729</v>
       </c>
       <c r="B20" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460449</v>
+        <v>460350</v>
       </c>
       <c r="R20" t="n">
-        <v>6990168</v>
+        <v>6990185</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2581,12 +2548,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Jättesälg!</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2601,65 +2573,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114576969</v>
+        <v>127028731</v>
       </c>
       <c r="B21" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460439</v>
+        <v>460347</v>
       </c>
       <c r="R21" t="n">
-        <v>6990168</v>
+        <v>6990068</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2683,12 +2650,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2703,64 +2670,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126287775</v>
+        <v>127028640</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460619</v>
+        <v>460576</v>
       </c>
       <c r="R22" t="n">
-        <v>6989872</v>
+        <v>6990272</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2784,27 +2747,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bitvis talrika förekomster, finns spritt i större delen av området. Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2813,7 +2761,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2832,51 +2779,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126287460</v>
+        <v>114578001</v>
       </c>
       <c r="B23" t="n">
-        <v>75075</v>
+        <v>57141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460522</v>
+        <v>460484</v>
       </c>
       <c r="R23" t="n">
-        <v>6989883</v>
+        <v>6990176</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2900,27 +2844,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2929,29 +2858,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126287351</v>
+        <v>126287283</v>
       </c>
       <c r="B24" t="n">
-        <v>98382</v>
+        <v>58817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,27 +2887,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>208249</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2987,13 +2916,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460494</v>
+        <v>460359</v>
       </c>
       <c r="R24" t="n">
-        <v>6989828</v>
+        <v>6989747</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3027,7 +2956,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Bitvis talrika förekomster, finns spritt i större delen av området. Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
+          <t>Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3055,51 +2984,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126287535</v>
+        <v>114577084</v>
       </c>
       <c r="B25" t="n">
-        <v>82792</v>
+        <v>99026</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>219788</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460539</v>
+        <v>460348</v>
       </c>
       <c r="R25" t="n">
-        <v>6989868</v>
+        <v>6989896</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3123,27 +3049,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3152,70 +3063,66 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126287420</v>
+        <v>114576968</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460597</v>
+        <v>460528</v>
       </c>
       <c r="R26" t="n">
-        <v>6989850</v>
+        <v>6990169</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3239,27 +3146,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3268,67 +3160,66 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127028746</v>
+        <v>114576969</v>
       </c>
       <c r="B27" t="n">
-        <v>80124</v>
+        <v>99035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460314</v>
+        <v>460439</v>
       </c>
       <c r="R27" t="n">
-        <v>6990069</v>
+        <v>6990168</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3352,12 +3243,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,60 +3263,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127028704</v>
+        <v>114576970</v>
       </c>
       <c r="B28" t="n">
-        <v>80123</v>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460394</v>
+        <v>460431</v>
       </c>
       <c r="R28" t="n">
-        <v>6990069</v>
+        <v>6990169</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3449,12 +3340,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3469,60 +3360,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028716</v>
+        <v>114576971</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>99035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460382</v>
+        <v>460394</v>
       </c>
       <c r="R29" t="n">
-        <v>6990158</v>
+        <v>6990175</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3546,12 +3437,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3566,60 +3457,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028668</v>
+        <v>114576973</v>
       </c>
       <c r="B30" t="n">
-        <v>98456</v>
+        <v>99035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460442</v>
+        <v>460368</v>
       </c>
       <c r="R30" t="n">
-        <v>6990074</v>
+        <v>6990205</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3643,12 +3534,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3663,60 +3554,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127028721</v>
+        <v>114576974</v>
       </c>
       <c r="B31" t="n">
-        <v>98456</v>
+        <v>99035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460361</v>
+        <v>460381</v>
       </c>
       <c r="R31" t="n">
-        <v>6990074</v>
+        <v>6990211</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3740,12 +3631,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3760,22 +3651,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127028719</v>
+        <v>114576975</v>
       </c>
       <c r="B32" t="n">
-        <v>98477</v>
+        <v>99035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3783,37 +3674,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460364</v>
+        <v>460388</v>
       </c>
       <c r="R32" t="n">
-        <v>6989926</v>
+        <v>6990220</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3837,12 +3728,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3857,60 +3748,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127028687</v>
+        <v>114577027</v>
       </c>
       <c r="B33" t="n">
-        <v>80123</v>
+        <v>99035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460422</v>
+        <v>460446</v>
       </c>
       <c r="R33" t="n">
-        <v>6990185</v>
+        <v>6989738</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3934,17 +3825,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Jättesälg!</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3959,22 +3845,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127028680</v>
+        <v>114577029</v>
       </c>
       <c r="B34" t="n">
-        <v>98477</v>
+        <v>99035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3982,37 +3868,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460426</v>
+        <v>460379</v>
       </c>
       <c r="R34" t="n">
-        <v>6990076</v>
+        <v>6989787</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4036,12 +3922,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4056,22 +3942,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127028702</v>
+        <v>114577030</v>
       </c>
       <c r="B35" t="n">
-        <v>98477</v>
+        <v>99035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4079,37 +3965,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460397</v>
+        <v>460481</v>
       </c>
       <c r="R35" t="n">
-        <v>6989975</v>
+        <v>6989926</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4133,12 +4019,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4153,60 +4039,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127028731</v>
+        <v>114577031</v>
       </c>
       <c r="B36" t="n">
-        <v>80123</v>
+        <v>99035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460347</v>
+        <v>460571</v>
       </c>
       <c r="R36" t="n">
-        <v>6990068</v>
+        <v>6989896</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4230,12 +4116,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4250,60 +4136,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127028693</v>
+        <v>114578349</v>
       </c>
       <c r="B37" t="n">
-        <v>80123</v>
+        <v>99142</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460419</v>
+        <v>460391</v>
       </c>
       <c r="R37" t="n">
-        <v>6990129</v>
+        <v>6990175</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4327,12 +4213,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4347,60 +4233,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127028632</v>
+        <v>114578350</v>
       </c>
       <c r="B38" t="n">
-        <v>80123</v>
+        <v>99142</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460580</v>
+        <v>460367</v>
       </c>
       <c r="R38" t="n">
-        <v>6990068</v>
+        <v>6990204</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4424,12 +4310,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4444,22 +4330,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127028631</v>
+        <v>126287775</v>
       </c>
       <c r="B39" t="n">
-        <v>98456</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4485,19 +4371,23 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460580</v>
+        <v>460619</v>
       </c>
       <c r="R39" t="n">
-        <v>6990166</v>
+        <v>6989872</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4521,12 +4411,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bitvis talrika förekomster, finns spritt i större delen av området. Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4535,6 +4440,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4553,32 +4459,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127028658</v>
+        <v>127028631</v>
       </c>
       <c r="B40" t="n">
-        <v>98477</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4494,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460450</v>
+        <v>460580</v>
       </c>
       <c r="R40" t="n">
-        <v>6989987</v>
+        <v>6990166</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4650,32 +4556,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127028700</v>
+        <v>127028668</v>
       </c>
       <c r="B41" t="n">
-        <v>98477</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4685,10 +4591,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460399</v>
+        <v>460442</v>
       </c>
       <c r="R41" t="n">
-        <v>6990025</v>
+        <v>6990074</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4747,32 +4653,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127028647</v>
+        <v>127028682</v>
       </c>
       <c r="B42" t="n">
-        <v>98477</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4782,10 +4688,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460528</v>
+        <v>460426</v>
       </c>
       <c r="R42" t="n">
-        <v>6990066</v>
+        <v>6990071</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4844,32 +4750,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127028726</v>
+        <v>127028692</v>
       </c>
       <c r="B43" t="n">
-        <v>98477</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4879,10 +4785,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460354</v>
+        <v>460419</v>
       </c>
       <c r="R43" t="n">
-        <v>6989926</v>
+        <v>6990164</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4941,32 +4847,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127028734</v>
+        <v>127028711</v>
       </c>
       <c r="B44" t="n">
-        <v>98477</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4976,10 +4882,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>460341</v>
+        <v>460385</v>
       </c>
       <c r="R44" t="n">
-        <v>6990066</v>
+        <v>6990183</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5038,32 +4944,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127028626</v>
+        <v>127028716</v>
       </c>
       <c r="B45" t="n">
-        <v>80123</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5073,10 +4979,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>460596</v>
+        <v>460382</v>
       </c>
       <c r="R45" t="n">
-        <v>6990129</v>
+        <v>6990158</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5135,32 +5041,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127028755</v>
+        <v>127028721</v>
       </c>
       <c r="B46" t="n">
-        <v>98477</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5170,10 +5076,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460239</v>
+        <v>460361</v>
       </c>
       <c r="R46" t="n">
-        <v>6990025</v>
+        <v>6990074</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5232,10 +5138,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127028692</v>
+        <v>127028737</v>
       </c>
       <c r="B47" t="n">
-        <v>98456</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5267,10 +5173,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460419</v>
+        <v>460333</v>
       </c>
       <c r="R47" t="n">
-        <v>6990164</v>
+        <v>6990071</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5329,32 +5235,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127028750</v>
+        <v>127028738</v>
       </c>
       <c r="B48" t="n">
-        <v>80124</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5364,10 +5270,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460302</v>
+        <v>460328</v>
       </c>
       <c r="R48" t="n">
-        <v>6990069</v>
+        <v>6990164</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5426,48 +5332,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127028634</v>
+        <v>114577495</v>
       </c>
       <c r="B49" t="n">
-        <v>80123</v>
+        <v>97983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460576</v>
+        <v>460520</v>
       </c>
       <c r="R49" t="n">
-        <v>6990197</v>
+        <v>6990168</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5491,12 +5397,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5511,60 +5417,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127028682</v>
+        <v>114577496</v>
       </c>
       <c r="B50" t="n">
-        <v>98456</v>
+        <v>97983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>460426</v>
+        <v>460449</v>
       </c>
       <c r="R50" t="n">
-        <v>6990071</v>
+        <v>6990168</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5588,12 +5494,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5608,60 +5514,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127028737</v>
+        <v>114577528</v>
       </c>
       <c r="B51" t="n">
-        <v>98456</v>
+        <v>97983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>460333</v>
+        <v>460355</v>
       </c>
       <c r="R51" t="n">
-        <v>6990071</v>
+        <v>6989828</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5685,12 +5591,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5705,22 +5611,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127028741</v>
+        <v>114578386</v>
       </c>
       <c r="B52" t="n">
-        <v>98477</v>
+        <v>99140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5748,17 +5654,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>460325</v>
+        <v>460534</v>
       </c>
       <c r="R52" t="n">
-        <v>6990076</v>
+        <v>6990169</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5782,12 +5688,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5802,60 +5708,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127028711</v>
+        <v>114578387</v>
       </c>
       <c r="B53" t="n">
-        <v>98456</v>
+        <v>99140</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460385</v>
+        <v>460507</v>
       </c>
       <c r="R53" t="n">
-        <v>6990183</v>
+        <v>6990170</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5879,12 +5785,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5899,60 +5805,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127028723</v>
+        <v>114578388</v>
       </c>
       <c r="B54" t="n">
-        <v>80123</v>
+        <v>99140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rammflon, Jmt</t>
+          <t>Myrviken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460357</v>
+        <v>460434</v>
       </c>
       <c r="R54" t="n">
-        <v>6989952</v>
+        <v>6990169</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5976,12 +5882,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5996,60 +5902,64 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Via Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127028695</v>
+        <v>126287351</v>
       </c>
       <c r="B55" t="n">
-        <v>80123</v>
+        <v>99140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rammflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460416</v>
+        <v>460494</v>
       </c>
       <c r="R55" t="n">
-        <v>6990144</v>
+        <v>6989828</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6073,12 +5983,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Bitvis talrika förekomster, finns spritt i större delen av området. Svårt med noggrannheten nyttja AFs app och GPS strulade så satte den lägre precision.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6087,6 +6002,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6102,6 +6018,1267 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127028647</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>460528</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6990066</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127028658</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>460450</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6989987</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127028659</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>460446</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6990282</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127028680</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>460426</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6990076</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127028700</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>460399</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6990025</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127028702</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>460397</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6989975</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127028719</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>460364</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6989926</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127028725</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>460355</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6990163</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127028726</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>460354</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6989926</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127028734</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>460341</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6990066</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127028741</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>460325</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6990076</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127028755</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>460239</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6990025</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127028757</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Rammflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>460144</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6989987</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
